--- a/data/trans_camb/P16-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 17,09</t>
+          <t>6,36; 16,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,64</t>
+          <t>4,16; 14,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 20,14</t>
+          <t>9,14; 20,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 16,34</t>
+          <t>6,74; 17,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,34</t>
+          <t>5,14; 15,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,67</t>
+          <t>2,47; 12,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,15</t>
+          <t>7,66; 15,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 13,58</t>
+          <t>6,2; 13,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,72</t>
+          <t>7,62; 14,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,21; 45,13</t>
+          <t>14,75; 43,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 38,34</t>
+          <t>9,82; 38,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,25; 53,23</t>
+          <t>21,23; 52,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 29,93</t>
+          <t>11,14; 31,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 28,47</t>
+          <t>8,2; 27,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 23,19</t>
+          <t>4,22; 22,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 31,79</t>
+          <t>15,02; 32,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 28,67</t>
+          <t>12,51; 29,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,1; 30,99</t>
+          <t>14,97; 31,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 13,64</t>
+          <t>3,81; 12,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,5</t>
+          <t>3,27; 11,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 7,24</t>
+          <t>-24,2; 7,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,63</t>
+          <t>7,22; 16,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 10,25</t>
+          <t>1,9; 10,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 8,85</t>
+          <t>0,48; 8,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,44</t>
+          <t>6,93; 13,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,3</t>
+          <t>3,9; 9,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 6,11</t>
+          <t>-18,58; 6,33</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 35,73</t>
+          <t>8,77; 33,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 31,45</t>
+          <t>7,47; 30,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 18,02</t>
+          <t>-58,32; 18,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 27,47</t>
+          <t>11,93; 29,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 18,13</t>
+          <t>3,33; 19,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 15,69</t>
+          <t>0,73; 15,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,84; 27,56</t>
+          <t>13,29; 27,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 21,06</t>
+          <t>7,44; 20,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,81; 12,29</t>
+          <t>-36,0; 12,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,98</t>
+          <t>3,59; 14,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 12,79</t>
+          <t>2,16; 13,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 20,81</t>
+          <t>9,05; 20,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 15,06</t>
+          <t>5,17; 15,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 8,99</t>
+          <t>-1,24; 8,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 27,01</t>
+          <t>-2,63; 27,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 13,19</t>
+          <t>5,26; 12,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,14</t>
+          <t>1,73; 9,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 26,27</t>
+          <t>5,63; 26,11</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 38,2</t>
+          <t>8,63; 40,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 35,76</t>
+          <t>5,06; 36,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,04; 58,06</t>
+          <t>21,87; 56,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,3; 27,9</t>
+          <t>8,55; 27,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 16,55</t>
+          <t>-2,06; 15,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 49,16</t>
+          <t>-4,42; 51,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,01; 27,96</t>
+          <t>10,3; 27,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 19,71</t>
+          <t>3,41; 20,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 55,21</t>
+          <t>11,35; 54,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 15,01</t>
+          <t>6,37; 15,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 16,68</t>
+          <t>8,21; 17,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 20,73</t>
+          <t>11,52; 20,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,47; 17,38</t>
+          <t>9,3; 17,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 10,35</t>
+          <t>1,41; 9,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,35</t>
+          <t>5,04; 16,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 15,29</t>
+          <t>9,14; 15,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,12</t>
+          <t>5,89; 11,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,33; 17,44</t>
+          <t>8,96; 17,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,09; 38,35</t>
+          <t>14,66; 41,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,79; 43,01</t>
+          <t>19,04; 44,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,77; 53,99</t>
+          <t>27,14; 53,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,08; 30,29</t>
+          <t>15,19; 30,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 18,2</t>
+          <t>1,99; 17,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,96; 28,12</t>
+          <t>8,26; 28,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,6; 31,42</t>
+          <t>17,47; 31,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 24,81</t>
+          <t>11,57; 24,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,75</t>
+          <t>17,44; 35,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,38</t>
+          <t>7,47; 12,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,68</t>
+          <t>6,78; 11,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,28</t>
+          <t>-2,13; 13,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,02</t>
+          <t>9,3; 14,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,51</t>
+          <t>3,73; 8,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,35</t>
+          <t>4,11; 13,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,56</t>
+          <t>9,18; 12,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,16; 9,49</t>
+          <t>6,03; 9,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,91</t>
+          <t>1,74; 11,9</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,8; 31,66</t>
+          <t>18,09; 32,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16,35; 29,76</t>
+          <t>16,38; 30,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 32,95</t>
+          <t>-5,12; 34,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,46; 24,38</t>
+          <t>15,6; 24,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,26; 14,95</t>
+          <t>6,23; 15,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,37; 24,58</t>
+          <t>6,87; 24,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,04; 25,76</t>
+          <t>18,0; 25,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,39</t>
+          <t>12,01; 19,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,19; 24,2</t>
+          <t>3,46; 24,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,45</t>
+          <t>14,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,41</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,1</t>
+          <t>10,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 16,49</t>
+          <t>6,02; 16,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 14,58</t>
+          <t>3,86; 14,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 20,3</t>
+          <t>8,77; 19,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,14</t>
+          <t>5,27; 16,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 15,28</t>
+          <t>4,82; 15,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 12,29</t>
+          <t>1,6; 11,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,23</t>
+          <t>7,26; 15,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,7</t>
+          <t>6,32; 14,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 14,84</t>
+          <t>6,75; 14,1</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 43,39</t>
+          <t>13,41; 41,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 38,01</t>
+          <t>8,58; 38,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,23; 52,12</t>
+          <t>20,21; 51,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 31,64</t>
+          <t>8,6; 30,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 27,62</t>
+          <t>7,99; 28,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 22,87</t>
+          <t>2,7; 20,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 32,48</t>
+          <t>14,29; 32,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 29,8</t>
+          <t>12,67; 30,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 31,93</t>
+          <t>13,42; 30,49</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>4,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 12,9</t>
+          <t>4,38; 13,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 11,88</t>
+          <t>3,15; 12,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,2; 7,33</t>
+          <t>0,76; 10,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,4</t>
+          <t>7,83; 15,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,87</t>
+          <t>1,57; 10,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 8,71</t>
+          <t>-0,78; 8,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,26</t>
+          <t>7,04; 13,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,96</t>
+          <t>3,63; 10,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 6,33</t>
+          <t>1,63; 8,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,24%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 33,45</t>
+          <t>9,86; 34,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 30,37</t>
+          <t>7,3; 31,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,32; 18,02</t>
+          <t>1,75; 25,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 29,03</t>
+          <t>12,87; 28,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 19,46</t>
+          <t>2,55; 17,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 15,49</t>
+          <t>-1,22; 14,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 27,33</t>
+          <t>13,51; 27,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 20,41</t>
+          <t>6,98; 20,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 12,76</t>
+          <t>3,11; 16,6</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15,18</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,12</t>
+          <t>8,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 14,41</t>
+          <t>3,09; 13,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 13,26</t>
+          <t>2,31; 13,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,7</t>
+          <t>8,66; 19,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,01</t>
+          <t>4,22; 14,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,34</t>
+          <t>-1,14; 8,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 27,6</t>
+          <t>-2,69; 7,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 12,92</t>
+          <t>5,73; 13,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,56</t>
+          <t>1,65; 8,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 26,11</t>
+          <t>4,41; 11,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,63; 40,31</t>
+          <t>7,23; 37,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 36,45</t>
+          <t>5,51; 35,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,87; 56,73</t>
+          <t>20,64; 53,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,55; 27,12</t>
+          <t>7,09; 27,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 15,24</t>
+          <t>-1,82; 15,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 51,35</t>
+          <t>-4,47; 13,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,3; 27,67</t>
+          <t>11,31; 28,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 20,43</t>
+          <t>3,26; 19,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,35; 54,94</t>
+          <t>8,67; 25,66</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16,03</t>
+          <t>14,71</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,79</t>
+          <t>10,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 15,74</t>
+          <t>6,31; 15,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,24</t>
+          <t>8,33; 17,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,52; 20,71</t>
+          <t>9,95; 19,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,3; 17,5</t>
+          <t>9,13; 17,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,94</t>
+          <t>1,27; 10,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 16,33</t>
+          <t>1,88; 10,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 15,53</t>
+          <t>8,91; 15,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 11,89</t>
+          <t>5,93; 12,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,96; 17,1</t>
+          <t>7,46; 13,69</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,66; 41,27</t>
+          <t>14,93; 40,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,04; 44,92</t>
+          <t>19,59; 45,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,14; 53,87</t>
+          <t>22,27; 49,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,19; 30,96</t>
+          <t>14,8; 29,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 17,24</t>
+          <t>1,92; 18,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,26; 28,12</t>
+          <t>2,97; 18,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,47; 31,65</t>
+          <t>17,33; 31,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,57; 24,61</t>
+          <t>11,6; 25,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,44; 35,02</t>
+          <t>14,45; 28,22</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,76</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>8,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,47</t>
+          <t>7,44; 12,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,73</t>
+          <t>6,74; 11,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 13,64</t>
+          <t>8,98; 14,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,3; 14,03</t>
+          <t>9,34; 13,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,57</t>
+          <t>3,98; 8,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,91</t>
+          <t>2,65; 6,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,61</t>
+          <t>9,34; 12,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,32</t>
+          <t>6,08; 9,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,9</t>
+          <t>6,63; 10,12</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18,09; 32,01</t>
+          <t>17,97; 32,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>16,38; 30,12</t>
+          <t>16,15; 29,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 34,21</t>
+          <t>21,57; 36,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,48</t>
+          <t>15,5; 24,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,23; 15,09</t>
+          <t>6,57; 15,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,87; 24,0</t>
+          <t>4,48; 12,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,0; 25,78</t>
+          <t>18,55; 26,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12,01; 19,11</t>
+          <t>11,98; 19,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,46; 24,17</t>
+          <t>13,19; 20,79</t>
         </is>
       </c>
     </row>
